--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:24:01+00:00</t>
+    <t>2026-01-29T14:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:26:05+00:00</t>
+    <t>2026-01-29T16:17:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T16:17:46+00:00</t>
+    <t>2026-01-29T16:25:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T16:25:01+00:00</t>
+    <t>2026-01-29T16:26:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T16:26:55+00:00</t>
+    <t>2026-01-29T16:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T16:54:52+00:00</t>
+    <t>2026-01-29T17:13:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T17:13:52+00:00</t>
+    <t>2026-01-29T17:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T17:15:24+00:00</t>
+    <t>2026-01-29T17:16:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T17:16:08+00:00</t>
+    <t>2026-01-30T09:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:23:26+00:00</t>
+    <t>2026-01-30T09:29:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/nr-publish-3.1.1-ballot/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:29:11+00:00</t>
+    <t>2026-01-30T09:35:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
